--- a/AAII_Financials/Quarterly/ARRPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARRPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
   <si>
     <t>ARRPY</t>
   </si>
@@ -656,76 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,8 +773,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +820,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +867,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +890,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +933,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +980,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1027,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1074,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,8 +1094,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1083,8 +1137,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1124,8 +1184,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1207,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,8 +1250,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1223,8 +1297,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,8 +1344,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1305,8 +1391,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1438,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,8 +1485,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1428,8 +1532,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1469,8 +1579,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1626,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1673,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1720,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1767,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1674,8 +1814,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1715,8 +1861,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,8 +1908,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1797,54 +1955,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +2030,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,377 +2049,433 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2891600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2918300</v>
+      </c>
+      <c r="F41" s="3">
         <v>2221400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2219900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2044600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1881800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2027100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2183800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2049700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2063900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2589800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2479900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2457400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2445700</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>133700</v>
+      </c>
+      <c r="F42" s="3">
         <v>153800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>153700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>232500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>214000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>216400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>233100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>132900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>133800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>224400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>214900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>193200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>192300</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1750300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1766400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1707200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1706000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1741600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1602900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1405900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1514600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1556800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1567600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1465700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1403500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1517500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1510200</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>171800</v>
+      </c>
+      <c r="F44" s="3">
         <v>173800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>173600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>171500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>157800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>141800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>152800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>151100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>152100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>127100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>121700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>138600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1279600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1291400</v>
+      </c>
+      <c r="F45" s="3">
         <v>62200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>62200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>77500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>71300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>63200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>68000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>88900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>89500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>85100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>81500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>168100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>167300</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6284700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6342700</v>
+      </c>
+      <c r="F46" s="3">
         <v>4361900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4358800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4342900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3997000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3920700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4223700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4051200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4079200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4546300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4353300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4534900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4513300</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1814200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1831000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1964300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1962900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2126800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1957400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2023000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2179300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2378700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2395100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2411800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2309500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2358100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2346800</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10975700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>11076900</v>
+      </c>
+      <c r="F48" s="3">
         <v>11007400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>10999600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>10711700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>9858400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>9627300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>10371400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>9498600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>9564100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9567800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>9161700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>9107000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>9063500</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3932400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3968600</v>
+      </c>
+      <c r="F49" s="3">
         <v>4101200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4098300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4164400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3832700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3327500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3584700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3184400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3206400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3163500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3029200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3182300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3167100</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2515,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2562,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1040800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1050400</v>
+      </c>
+      <c r="F52" s="3">
         <v>2112200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2110800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1921300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1768300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1798300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1937300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1976900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1990500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1857000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1778200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1452000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1445000</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2656,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24307100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>24531300</v>
+      </c>
+      <c r="F54" s="3">
         <v>23795900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>23779200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>23490300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>21619100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>20891400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>22506100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>21289000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>21436000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>21731000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>20808600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>20796900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>20697500</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2726,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,254 +2745,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>459300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>463500</v>
+      </c>
+      <c r="F57" s="3">
         <v>469600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>469300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>806800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>742500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>455500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>490700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>467200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>470400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>655500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>627600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>619000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>616000</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2344300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2366000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2215600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2214000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1214300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1117600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1890500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2036600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1915800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1929000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2088000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1999400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2233600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2222900</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1332100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1344400</v>
+      </c>
+      <c r="F59" s="3">
         <v>1399600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1398600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>941900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>866800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1090200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1174400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1121800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1129600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1286600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1232000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1136500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1131000</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4974300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5020200</v>
+      </c>
+      <c r="F60" s="3">
         <v>4880800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4877400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3866100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3558100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4142300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4462400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4286900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4316500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4670100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4471800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>4632100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>4610000</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10971100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>11072300</v>
+      </c>
+      <c r="F61" s="3">
         <v>10247700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>10240500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11224900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10330700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>9200700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>9911900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>9403200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>9468100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>9418600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>9018800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9132100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>9088400</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>824900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>832500</v>
+      </c>
+      <c r="F62" s="3">
         <v>866500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>865900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>979400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>901400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>736100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>793000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>757500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>762800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>766000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>733500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>791500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>787700</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +3070,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +3117,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3164,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18223500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>18391600</v>
+      </c>
+      <c r="F66" s="3">
         <v>17448600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>17436300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>17522000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>16126200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>15184800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>16358500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>15487000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>15593900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>15876000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>15202200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>15588400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>15513900</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3234,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3277,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3324,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3371,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3418,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4348200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4388300</v>
+      </c>
+      <c r="F72" s="3">
         <v>4566200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4562900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4261900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3922400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3947600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4252700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4045900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4073800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4206900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4028400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3695400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3677700</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3512,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3559,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3606,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4925200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4970600</v>
+      </c>
+      <c r="F76" s="3">
         <v>5102700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5099100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4777500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4396900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4570900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4924200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4684500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4716800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4822600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4617900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4347200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4326400</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,54 +3700,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3409,8 +3799,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +3822,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>278300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>256200</v>
+      </c>
+      <c r="F83" s="3">
         <v>187400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>201900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>205200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>206600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>227700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>218000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>208000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>207000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>187600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>172100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>140600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>149400</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3912,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3959,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +4006,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +4053,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +4100,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>395900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>399500</v>
+      </c>
+      <c r="F89" s="3">
         <v>507200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>506900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>454500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>418300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>454000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>489100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>346600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>349000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>500700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>479500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>371700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>369900</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +4170,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-299300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-302100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-429700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-429400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-268900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-247500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-304400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-327900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-242700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-244400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-347100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-332300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-185600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-184700</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4260,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4307,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-189100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-190800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-304100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-303900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-289500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-266400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-440500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-474600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-326800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-329100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-202300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-193700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-425200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-423200</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,49 +4377,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>214800</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>216800</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>173800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>160000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>202000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>203400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>168700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>167900</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4467,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4514,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,127 +4561,151 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>151400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>152800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-112700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-112600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-277700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-255600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>6200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>6700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-251800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-253500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-245400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-235000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-151200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-150500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="F101" s="3">
         <v>3100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>3300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-2100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-3300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-3300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>4200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>362700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>366100</v>
+      </c>
+      <c r="F102" s="3">
         <v>91600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>91500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-130900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-120500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>22800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>24500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-230400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-232000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>50800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>48700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-208000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-207000</v>
       </c>
     </row>
